--- a/artfynd/A 44214-2025 artfynd.xlsx
+++ b/artfynd/A 44214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128374499</v>
       </c>
       <c r="B2" t="n">
-        <v>90891</v>
+        <v>90983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44214-2025 artfynd.xlsx
+++ b/artfynd/A 44214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128374499</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>90995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44214-2025 artfynd.xlsx
+++ b/artfynd/A 44214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128374499</v>
       </c>
       <c r="B2" t="n">
-        <v>90995</v>
+        <v>90997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44214-2025 artfynd.xlsx
+++ b/artfynd/A 44214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128374499</v>
       </c>
       <c r="B2" t="n">
-        <v>90997</v>
+        <v>90998</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44214-2025 artfynd.xlsx
+++ b/artfynd/A 44214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128374499</v>
       </c>
       <c r="B2" t="n">
-        <v>90998</v>
+        <v>91025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44214-2025 artfynd.xlsx
+++ b/artfynd/A 44214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128374499</v>
       </c>
       <c r="B2" t="n">
-        <v>91025</v>
+        <v>91035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44214-2025 artfynd.xlsx
+++ b/artfynd/A 44214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128374499</v>
       </c>
       <c r="B2" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44214-2025 artfynd.xlsx
+++ b/artfynd/A 44214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128374499</v>
       </c>
       <c r="B2" t="n">
-        <v>91039</v>
+        <v>91044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44214-2025 artfynd.xlsx
+++ b/artfynd/A 44214-2025 artfynd.xlsx
@@ -675,38 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128374499</v>
+        <v>133813909</v>
       </c>
       <c r="B2" t="n">
-        <v>91046</v>
+        <v>57925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6039941</v>
+        <v>102110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Abborrtjärnen, Jmt</t>
@@ -743,17 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca 140-årig gles tallskog på mager lavmark. Medelstor, ljusgul, geléaktig konsistens, klibbig och föll lätt isär.</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,7 +763,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133813909</v>
+        <v>128374499</v>
       </c>
       <c r="B3" t="n">
-        <v>57925</v>
+        <v>91431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,33 +792,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102110</v>
+        <v>6039941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Gelatinfingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Ramaria primulina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Abborrtjärnen, Jmt</t>
@@ -855,12 +849,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ca 140-årig gles tallskog på mager lavmark. Medelstor, ljusgul, geléaktig konsistens, klibbig och föll lätt isär.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44214-2025 artfynd.xlsx
+++ b/artfynd/A 44214-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133813909</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128374499</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>